--- a/VerveStacks_ZAF_grids_kan/BY_Trans.xlsx
+++ b/VerveStacks_ZAF_grids_kan/BY_Trans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\assumptions\VerveStacks_ISO_template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D1EB1B-B45C-4149-AEE2-7B3180C9E8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C66D1A-E30F-4211-9B97-97CB335D82CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc." sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="62">
   <si>
     <t>attribute</t>
   </si>
@@ -205,13 +205,28 @@
   </si>
   <si>
     <t>*_hydro_ps*</t>
+  </si>
+  <si>
+    <t>~TFM_UPD</t>
+  </si>
+  <si>
+    <t>Eff</t>
+  </si>
+  <si>
+    <t>*.9</t>
+  </si>
+  <si>
+    <t>ep_coal_super*</t>
+  </si>
+  <si>
+    <t>these are aircooled plants</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,6 +246,15 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -276,11 +300,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Heading 2" xfId="1" builtinId="17"/>
@@ -617,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{982CB9B3-DA63-443B-9AA5-BEE16CBC2D59}">
-  <dimension ref="B3:L25"/>
+  <dimension ref="B3:L30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.53125" bestFit="1" customWidth="1"/>
@@ -839,12 +864,12 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:7" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B20" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="2:7" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B21" s="1" t="s">
         <v>0</v>
       </c>
@@ -858,7 +883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
         <v>48</v>
       </c>
@@ -872,7 +897,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
         <v>48</v>
       </c>
@@ -886,7 +911,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
         <v>48</v>
       </c>
@@ -900,7 +925,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>48</v>
       </c>
@@ -912,6 +937,36 @@
       </c>
       <c r="E25" s="3" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B28" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_ZAF_grids_kan/BY_Trans.xlsx
+++ b/VerveStacks_ZAF_grids_kan/BY_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C66D1A-E30F-4211-9B97-97CB335D82CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C80247-D3FA-48F8-840D-11131F5365B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="186">
   <si>
     <t>attribute</t>
   </si>
@@ -207,26 +207,401 @@
     <t>*_hydro_ps*</t>
   </si>
   <si>
-    <t>~TFM_UPD</t>
-  </si>
-  <si>
-    <t>Eff</t>
-  </si>
-  <si>
-    <t>*.9</t>
-  </si>
-  <si>
-    <t>ep_coal_super*</t>
-  </si>
-  <si>
-    <t>these are aircooled plants</t>
+    <t>ep_coal_subcritical_G100000100348</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100349</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100350</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100351</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100352</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000100353</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103807</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103808</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103810</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103811</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103812</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103813</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000103806</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000103809</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000103814</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000103815</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105828</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105829</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105830</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105831</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105832</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105833</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105834</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105835</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105836</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106726</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106727</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106728</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106729</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106730</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106731</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101168</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101169</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101170</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101171</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101172</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101173</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101174</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000101175</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103136</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103137</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000103138</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000103139</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000103140</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000103141</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105663</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105664</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105665</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105666</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105667</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105668</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105640</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105641</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105642</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105643</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105644</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105645</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105646</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105647</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105648</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105649</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105650</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105651</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105652</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105964</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105965</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105966</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105967</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105968</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000105969</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106039</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106040</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106041</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106042</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106043</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106044</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110396</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110397</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110398</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110399</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110400</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000110401</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106603</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106604</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106605</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106600</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106601</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106602</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106720</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106721</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106722</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106723</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106724</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106725</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102524</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102525</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102527</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102528</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000102529</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000102526</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106780</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106781</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106782</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106783</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106784</t>
+  </si>
+  <si>
+    <t>ep_coal_supercritical_G100000106785</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000113799</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000113800</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000113801</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000113802</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000113803</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000113804</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108568</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108569</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000108622</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000108623</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000108624</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000108625</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000108626</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106240</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106241</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106242</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106243</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106244</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000106245</t>
+  </si>
+  <si>
+    <t>*Current efficiency</t>
+  </si>
+  <si>
+    <t>EFF</t>
+  </si>
+  <si>
+    <t>Source: zaf_coal_efficiency_corrections.xlsx</t>
+  </si>
+  <si>
+    <t>~TFM_UPD-AT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -259,16 +634,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -294,18 +680,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Heading 2" xfId="1" builtinId="17"/>
@@ -642,10 +1048,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{982CB9B3-DA63-443B-9AA5-BEE16CBC2D59}">
-  <dimension ref="B3:L30"/>
+  <dimension ref="B3:L154"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="9.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.59765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.53125" customWidth="1"/>
     <col min="4" max="4" width="9.73046875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -864,12 +1270,12 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="20" spans="2:6" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B20" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="2:6" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B21" s="1" t="s">
         <v>0</v>
       </c>
@@ -883,7 +1289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
         <v>48</v>
       </c>
@@ -897,7 +1303,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
         <v>48</v>
       </c>
@@ -911,7 +1317,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
         <v>48</v>
       </c>
@@ -925,7 +1331,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>48</v>
       </c>
@@ -939,34 +1345,1398 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="28" spans="2:6" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B28" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="B29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B30" s="6" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="29" spans="2:7" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B29" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B30" t="s">
+      <c r="C30" s="7">
+        <v>0.36720000000000003</v>
+      </c>
+      <c r="D30" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B31" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C31" s="7">
+        <v>0.36720000000000003</v>
+      </c>
+      <c r="D31" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B32" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D30" t="s">
+      <c r="C32" s="7">
+        <v>0.36720000000000003</v>
+      </c>
+      <c r="D32" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B33" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="C33" s="7">
+        <v>0.36720000000000003</v>
+      </c>
+      <c r="D33" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B34" s="6" t="s">
         <v>61</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.36720000000000008</v>
+      </c>
+      <c r="D34" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B35" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.36720000000000008</v>
+      </c>
+      <c r="D35" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B36" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.34560000000000002</v>
+      </c>
+      <c r="D36" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B37" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.34560000000000002</v>
+      </c>
+      <c r="D37" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B38" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D38" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B39" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.34560000000000002</v>
+      </c>
+      <c r="D39" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B40" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.34560000000000002</v>
+      </c>
+      <c r="D40" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B41" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.34560000000000002</v>
+      </c>
+      <c r="D41" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B42" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="D42" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B43" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="D43" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B44" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="D44" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B45" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="D45" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B46" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C46" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D46" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B47" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C47" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D47" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B48" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C48" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D48" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B49" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C49" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D49" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B50" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C50" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D50" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B51" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C51" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D51" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B52" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C52" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D52" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B53" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C53" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D53" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B54" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D54" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B55" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.36720000000000003</v>
+      </c>
+      <c r="D55" s="7">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B56" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.36720000000000003</v>
+      </c>
+      <c r="D56" s="7">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B57" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.36720000000000003</v>
+      </c>
+      <c r="D57" s="7">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B58" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D58" s="7">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B59" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D59" s="7">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B60" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D60" s="7">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B61" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D61" s="7">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B62" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C62" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D62" s="7">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B63" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C63" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D63" s="7">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B64" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C64" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D64" s="7">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B65" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C65" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D65" s="7">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B66" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C66" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D66" s="7">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B67" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C67" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D67" s="7">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B68" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C68" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D68" s="7">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B69" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C69" s="7">
+        <v>0.34560000000000002</v>
+      </c>
+      <c r="D69" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B70" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C70" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D70" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B71" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C71" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D71" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B72" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C72" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="D72" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B73" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C73" s="7">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="D73" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B74" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C74" s="7">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="D74" s="7">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B75" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C75" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D75" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B76" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C76" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D76" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B77" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C77" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D77" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B78" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C78" s="7">
+        <v>0.38879999999999998</v>
+      </c>
+      <c r="D78" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B79" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C79" s="7">
+        <v>0.38879999999999998</v>
+      </c>
+      <c r="D79" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B80" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C80" s="7">
+        <v>0.38879999999999998</v>
+      </c>
+      <c r="D80" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B81" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C81" s="7">
+        <v>0.29160000000000003</v>
+      </c>
+      <c r="D81" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B82" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C82" s="7">
+        <v>0.29160000000000003</v>
+      </c>
+      <c r="D82" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B83" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C83" s="7">
+        <v>0.29160000000000003</v>
+      </c>
+      <c r="D83" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B84" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C84" s="7">
+        <v>0.29160000000000003</v>
+      </c>
+      <c r="D84" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B85" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C85" s="7">
+        <v>0.29160000000000003</v>
+      </c>
+      <c r="D85" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B86" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C86" s="7">
+        <v>0.29160000000000003</v>
+      </c>
+      <c r="D86" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B87" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C87" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D87" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B88" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C88" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D88" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B89" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C89" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D89" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B90" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C90" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D90" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B91" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C91" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D91" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B92" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C92" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D92" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B93" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C93" s="7">
+        <v>0.32400000000000001</v>
+      </c>
+      <c r="D93" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B94" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C94" s="7">
+        <v>0.36720000000000003</v>
+      </c>
+      <c r="D94" s="7">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B95" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C95" s="7">
+        <v>0.36720000000000003</v>
+      </c>
+      <c r="D95" s="7">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B96" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C96" s="7">
+        <v>0.36720000000000003</v>
+      </c>
+      <c r="D96" s="7">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B97" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C97" s="7">
+        <v>0.36720000000000003</v>
+      </c>
+      <c r="D97" s="7">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B98" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C98" s="7">
+        <v>0.36720000000000003</v>
+      </c>
+      <c r="D98" s="7">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B99" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C99" s="7">
+        <v>0.36720000000000003</v>
+      </c>
+      <c r="D99" s="7">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B100" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C100" s="7">
+        <v>0.44819999999999999</v>
+      </c>
+      <c r="D100" s="7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B101" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C101" s="7">
+        <v>0.44819999999999999</v>
+      </c>
+      <c r="D101" s="7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B102" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C102" s="7">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="D102" s="7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B103" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C103" s="7">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="D103" s="7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B104" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C104" s="7">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="D104" s="7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B105" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C105" s="7">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="D105" s="7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B106" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C106" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D106" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B107" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C107" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D107" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B108" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C108" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D108" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B109" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C109" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D109" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B110" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C110" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D110" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B111" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C111" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D111" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B112" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C112" s="7">
+        <v>0.38879999999999998</v>
+      </c>
+      <c r="D112" s="7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B113" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C113" s="7">
+        <v>0.38879999999999998</v>
+      </c>
+      <c r="D113" s="7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B114" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C114" s="7">
+        <v>0.38879999999999998</v>
+      </c>
+      <c r="D114" s="7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B115" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C115" s="7">
+        <v>0.38879999999999992</v>
+      </c>
+      <c r="D115" s="7">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B116" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C116" s="7">
+        <v>0.38879999999999992</v>
+      </c>
+      <c r="D116" s="7">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B117" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C117" s="7">
+        <v>0.38879999999999992</v>
+      </c>
+      <c r="D117" s="7">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B118" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C118" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D118" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B119" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C119" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D119" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B120" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C120" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D120" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B121" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C121" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D121" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B122" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C122" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D122" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B123" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C123" s="7">
+        <v>0.38879999999999992</v>
+      </c>
+      <c r="D123" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B124" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C124" s="7">
+        <v>0.36720000000000003</v>
+      </c>
+      <c r="D124" s="7">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B125" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C125" s="7">
+        <v>0.36720000000000003</v>
+      </c>
+      <c r="D125" s="7">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B126" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C126" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D126" s="7">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B127" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C127" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D127" s="7">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B128" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C128" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D128" s="7">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B129" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C129" s="7">
+        <v>0.315</v>
+      </c>
+      <c r="D129" s="7">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B130" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C130" s="7">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="D130" s="7">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B131" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C131" s="7">
+        <v>0.44819999999999999</v>
+      </c>
+      <c r="D131" s="7">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B132" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C132" s="7">
+        <v>0.44819999999999999</v>
+      </c>
+      <c r="D132" s="7">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B133" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C133" s="7">
+        <v>0.44819999999999999</v>
+      </c>
+      <c r="D133" s="7">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B134" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C134" s="7">
+        <v>0.44819999999999999</v>
+      </c>
+      <c r="D134" s="7">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B135" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C135" s="7">
+        <v>0.44819999999999999</v>
+      </c>
+      <c r="D135" s="7">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B136" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C136" s="7">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="D136" s="7">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B137" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C137" s="7">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="D137" s="7">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B138" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C138" s="7">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="D138" s="7">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B139" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C139" s="7">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="D139" s="7">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B140" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C140" s="7">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="D140" s="7">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B141" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C141" s="7">
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="D141" s="7">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B142" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C142" s="7">
+        <v>0.34560000000000002</v>
+      </c>
+      <c r="D142" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B143" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C143" s="7">
+        <v>0.34560000000000002</v>
+      </c>
+      <c r="D143" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B144" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C144" s="7">
+        <v>0.27000000000000007</v>
+      </c>
+      <c r="D144" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B145" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C145" s="7">
+        <v>0.27000000000000007</v>
+      </c>
+      <c r="D145" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B146" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C146" s="7">
+        <v>0.27000000000000007</v>
+      </c>
+      <c r="D146" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B147" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C147" s="7">
+        <v>0.27000000000000007</v>
+      </c>
+      <c r="D147" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B148" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C148" s="7">
+        <v>0.27000000000000007</v>
+      </c>
+      <c r="D148" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B149" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C149" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D149" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B150" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C150" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D150" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B151" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C151" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D151" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B152" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C152" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D152" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B153" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C153" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D153" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B154" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C154" s="7">
+        <v>0.378</v>
+      </c>
+      <c r="D154" s="7">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
